--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.2.文字コード.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.2.文字コード.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95804A0A-A7AE-4447-85AF-F68D3E2FD777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017B703D-0F7E-42DD-9F9B-CD0E4ADD83FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.2.文字コード" sheetId="12" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7.2.文字コード'!#REF!</definedName>
-    <definedName name="_Toc297797585" localSheetId="0">'7.2.文字コード'!$E$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'7.2.文字コード'!$A$1:$AI$58</definedName>
-    <definedName name="使用可能文字コード一覧">'7.2.文字コード'!$AM$7:$AM$19</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -25,6 +22,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -45,6 +44,16 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
+    <t>要件定義</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>作成</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -56,6 +65,9 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
+    <t>アプリケーション方式設計書</t>
+  </si>
+  <si>
     <t>変更</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -67,7 +79,8 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>アプリケーション方式設計書</t>
+    <t>7.</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>処理方式共通</t>
@@ -91,6 +104,53 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>原則、文字コード変換処理は本システム内で行う。他システムは、メッセージやファイルを本システムに送る際に文字コード変換を行う必要はない。</t>
+  </si>
+  <si>
+    <t>文字コード変換処理および特殊文字の変換は、ミドルウェア製品（例えばHULFT）の文字コード変換機能を使用して実現する。</t>
+    <rPh sb="27" eb="29">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>タト</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ヘンカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>また、Nablarchおよび共通コンポーネントでファイルを読み込む際は、必ず文字コードを指定して読み込む。</t>
+    <rPh sb="29" eb="30">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>システムで使用する文字コード</t>
     <rPh sb="5" eb="7">
       <t>シヨウ</t>
@@ -101,15 +161,61 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>文字コード変換方式</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>7.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ブラウザに表示する文字コード。</t>
+    <t>システム内で使用する文字種と文字コード</t>
+    <rPh sb="10" eb="13">
+      <t>モジシュ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>本システムでは、【使用可能文字種一覧】で定められた文字種のみを使用可能（使用許可文字種）とし、それ以外は禁止文字とする。</t>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="9" eb="16">
+      <t>シヨウカノウモジシュ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>サダ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シュ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>使用する文字コードは以下の通り。</t>
+    <rPh sb="0" eb="2">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>トオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>システム構成</t>
+    <rPh sb="4" eb="6">
+      <t>コウセイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -120,17 +226,14 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>システム構成</t>
-    <rPh sb="4" eb="6">
-      <t>コウセイ</t>
-    </rPh>
+    <t>ブラウザ</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>UTF-8</t>
   </si>
   <si>
-    <t>ブラウザ</t>
+    <t>ブラウザに表示する文字コード。</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -138,10 +241,18 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>DBに格納する文字コード。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>メール</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>UTF-8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>メール送信時の文字コード。</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -154,27 +265,59 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>画面表示JSPファイルの文字コード</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HTML</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>includeする静的コンテンツ</t>
+    <rPh sb="9" eb="11">
+      <t>セイテキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CSS</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CSSファイルの文字コード</t>
+    <rPh sb="8" eb="10">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>JavaScript</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>画面制御JavaScriptファイルの文字コード</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>SQL</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>UTF-8</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ログ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>CSS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>DBに格納する文字コード。</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -185,6 +328,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>ログ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>本システムで出力するログファイルの文字コード</t>
     <rPh sb="0" eb="1">
       <t>ホン</t>
@@ -198,73 +345,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>画面制御JavaScriptファイルの文字コード</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>セイギョ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>モジ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>CSSファイルの文字コード</t>
-    <rPh sb="8" eb="10">
-      <t>モジ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>画面表示JSPファイルの文字コード</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>モジ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>使用する文字コードは以下の通り。</t>
-    <rPh sb="0" eb="2">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>トオ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>要件定義</t>
-    <rPh sb="0" eb="2">
-      <t>ヨウケン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テイギ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>HTML</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>includeする静的コンテンツ</t>
-    <rPh sb="9" eb="11">
-      <t>セイテキ</t>
-    </rPh>
+    <t>JSON</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -282,6 +363,192 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>禁止文字、他システム禁止文字の取り扱い</t>
+    <rPh sb="10" eb="12">
+      <t>キンシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>特殊文字入力変換処理</t>
+  </si>
+  <si>
+    <t>ブラウザや他システムから禁止文字が入力された場合は、業務コンポーネントにて以下のようにエラー制御を行う。</t>
+    <rPh sb="5" eb="6">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>キンシモジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>接続先</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エラー制御</t>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>入力画面にエラーを返す。</t>
+  </si>
+  <si>
+    <t>他システム</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>接続先システムに応じて、下記のいずれかを選択する。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エラー通知や運用面も考慮して選択すること。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ファイル転送/外部媒体</t>
+  </si>
+  <si>
+    <t>エラーとして処理を中断する。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エラーとするが代替文字に変換し、処理を継続する。　</t>
+    <rPh sb="7" eb="9">
+      <t>ダイタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>特殊文字出力変換処理</t>
+  </si>
+  <si>
+    <t>本システムの使用許可文字種に含まれる文字のうち、接続先システムがファイル転送およびメッセージ連携において許容しない文字を、</t>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>シヨウキョカ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>モジシュ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>セツゾクサキ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>テンソウ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>キョヨウ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>他システム禁止文字と定義する。</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キンシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>他システム禁止文字は、代替文字（略字等）へ変換したうえで接続先システムに連携する。</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>キンシモジ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ダイタイモジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>リャクジ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>セツゾクサキ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>レンケイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>代替文字の変換ルールは、接続先ごとに個別テーブルを用意して管理する。</t>
+    <rPh sb="0" eb="4">
+      <t>ダイタイモジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>文字コード変換方式</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>文字コード変換方式概要</t>
     <rPh sb="0" eb="2">
       <t>モジ</t>
@@ -320,6 +587,36 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>変換対象</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>変換方式</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エラー時の挙動</t>
+    <rPh sb="3" eb="4">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>接続先システム２との連携</t>
     <rPh sb="0" eb="3">
       <t>セツゾクサキ</t>
@@ -330,26 +627,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>変換対象</t>
-    <rPh sb="0" eb="2">
-      <t>ヘンカン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>タイショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>変換方式</t>
-    <rPh sb="0" eb="2">
-      <t>ヘンカン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ホウシキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>HULFTのコード変換機能を利用</t>
     <rPh sb="9" eb="11">
       <t>ヘンカン</t>
@@ -376,297 +653,19 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>エラー時の挙動</t>
-    <rPh sb="3" eb="4">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キョドウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>特殊文字入力変換処理</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>入力画面にエラーを返す。</t>
-  </si>
-  <si>
-    <t>ファイル転送/外部媒体</t>
-  </si>
-  <si>
-    <t>特殊文字出力変換処理</t>
-  </si>
-  <si>
-    <t>接続先</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>・</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>接続先システムに応じて、下記のいずれかを選択する。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>エラー通知や運用面も考慮して選択すること。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>システム内で使用する文字種と文字コード</t>
-    <rPh sb="10" eb="13">
-      <t>モジシュ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>本システムでは、【使用可能文字種一覧】で定められた文字種のみを使用可能（使用許可文字種）とし、それ以外は禁止文字とする。</t>
-    <rPh sb="0" eb="1">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="9" eb="16">
-      <t>シヨウカノウモジシュ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>サダ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>シュ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>禁止文字、他システム禁止文字の取り扱い</t>
-    <rPh sb="10" eb="12">
-      <t>キンシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ブラウザや他システムから禁止文字が入力された場合は、業務コンポーネントにて以下のようにエラー制御を行う。</t>
-    <rPh sb="5" eb="6">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="12" eb="16">
-      <t>キンシモジ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>セイギョ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>他システム</t>
-    <rPh sb="0" eb="1">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>エラー制御</t>
-    <rPh sb="3" eb="5">
-      <t>セイギョ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>他システム禁止文字と定義する。</t>
-    <rPh sb="0" eb="1">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キンシ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>テイギ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>本システムの使用許可文字種に含まれる文字のうち、接続先システムがファイル転送およびメッセージ連携において許容しない文字を、</t>
-    <rPh sb="0" eb="1">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>シヨウキョカ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>モジシュ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>フク</t>
+    <t>送受信するデータの文字コード</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>入力処理方式(REST)、メッセージ仕向け(HTTP/HTTPS)および非同期でブラウザと</t>
+    <rPh sb="0" eb="6">
+      <t>ニュウリョクショリホウシキ</t>
     </rPh>
     <rPh sb="18" eb="20">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="24" eb="27">
-      <t>セツゾクサキ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>テンソウ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>レンケイ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>キョヨウ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>モジ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>代替文字の変換ルールは、接続先ごとに個別テーブルを用意して管理する。</t>
-    <rPh sb="0" eb="4">
-      <t>ダイタイモジ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヘンカン</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>エラーとするが代替文字に変換し、処理を継続する。　</t>
-    <rPh sb="7" eb="9">
-      <t>ダイタイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>他システム禁止文字は、代替文字（略字等）へ変換したうえで接続先システムに連携する。</t>
-    <rPh sb="0" eb="1">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="5" eb="9">
-      <t>キンシモジ</t>
-    </rPh>
-    <rPh sb="11" eb="15">
-      <t>ダイタイモジ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>リャクジ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ヘンカン</t>
-    </rPh>
-    <rPh sb="28" eb="31">
-      <t>セツゾクサキ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>レンケイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>エラーとして処理を中断する。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>JSON</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>メッセージ仕向け(HTTP/HTTPS)および非同期でブラウザと送受信するデータの</t>
-    <rPh sb="5" eb="7">
       <t>シム</t>
     </rPh>
-    <rPh sb="23" eb="26">
+    <rPh sb="36" eb="39">
       <t>ヒドウキ</t>
-    </rPh>
-    <rPh sb="32" eb="35">
-      <t>ソウジュシン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>文字コード</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>原則、文字コード変換処理は本システム内で行う。他システムは、メッセージやファイルを本システムに送る際に文字コード変換を行う必要はない。</t>
-  </si>
-  <si>
-    <t>文字コード変換処理および特殊文字の変換は、ミドルウェア製品（例えばHULFT）の文字コード変換機能を使用して実現する。</t>
-    <rPh sb="27" eb="29">
-      <t>セイヒン</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>タト</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ヘンカン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>また、Nablarchおよび共通コンポーネントでファイルを読み込む際は、必ず文字コードを指定して読み込む。</t>
-    <rPh sb="29" eb="30">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>カナラ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>コ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2395,47 +2394,47 @@
     </xf>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -2450,9 +2449,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2471,28 +2467,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2508,9 +2501,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
@@ -2528,25 +2518,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2555,15 +2539,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2582,23 +2560,59 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2618,53 +2632,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="226">
@@ -3229,7 +3198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI57"/>
@@ -3247,137 +3216,137 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="83"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="60"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="84" t="s">
-        <v>37</v>
-      </c>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
-      <c r="V1" s="85"/>
-      <c r="W1" s="85"/>
-      <c r="X1" s="86"/>
+      <c r="R1" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="63"/>
       <c r="Y1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="75"/>
-      <c r="AC1" s="75"/>
-      <c r="AD1" s="75"/>
-      <c r="AE1" s="76"/>
-      <c r="AF1" s="62"/>
-      <c r="AG1" s="63"/>
-      <c r="AH1" s="63"/>
-      <c r="AI1" s="64"/>
+      <c r="AA1" s="64"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="66"/>
+      <c r="AF1" s="70"/>
+      <c r="AG1" s="71"/>
+      <c r="AH1" s="71"/>
+      <c r="AI1" s="72"/>
     </row>
     <row r="2" spans="1:35" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="67"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="60"/>
       <c r="P2" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q2" s="8"/>
-      <c r="R2" s="68" t="s">
-        <v>8</v>
-      </c>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="69"/>
-      <c r="W2" s="69"/>
-      <c r="X2" s="70"/>
+      <c r="R2" s="73" t="s">
+        <v>6</v>
+      </c>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="75"/>
       <c r="Y2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="74"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="75"/>
-      <c r="AD2" s="75"/>
-      <c r="AE2" s="76"/>
-      <c r="AF2" s="62"/>
-      <c r="AG2" s="63"/>
-      <c r="AH2" s="63"/>
-      <c r="AI2" s="64"/>
+      <c r="AA2" s="64"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="66"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="71"/>
+      <c r="AH2" s="71"/>
+      <c r="AI2" s="72"/>
     </row>
     <row r="3" spans="1:35" ht="14.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="12"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="72"/>
-      <c r="U3" s="72"/>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="73"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="W3" s="77"/>
+      <c r="X3" s="78"/>
       <c r="Y3" s="11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z3" s="13"/>
-      <c r="AA3" s="74"/>
-      <c r="AB3" s="75"/>
-      <c r="AC3" s="75"/>
-      <c r="AD3" s="75"/>
-      <c r="AE3" s="76"/>
-      <c r="AF3" s="62"/>
-      <c r="AG3" s="63"/>
-      <c r="AH3" s="63"/>
-      <c r="AI3" s="64"/>
+      <c r="AA3" s="64"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="66"/>
+      <c r="AF3" s="70"/>
+      <c r="AG3" s="71"/>
+      <c r="AH3" s="71"/>
+      <c r="AI3" s="72"/>
     </row>
     <row r="4" spans="1:35" ht="14.1" customHeight="1"/>
     <row r="5" spans="1:35" ht="14.1" customHeight="1">
       <c r="B5" s="14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="14.1" customHeight="1"/>
@@ -3387,7 +3356,7 @@
         <v>7.2.</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="14.1" customHeight="1"/>
@@ -3397,23 +3366,23 @@
         <v>7.2.1.</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="14.1" customHeight="1">
       <c r="D10" s="14"/>
       <c r="E10" s="17" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:35" ht="14.1" customHeight="1">
       <c r="E11" s="17" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:35" ht="14.1" customHeight="1">
       <c r="E12" s="17" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:35" ht="14.1" customHeight="1">
@@ -3425,7 +3394,7 @@
         <v>7.2.2.</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:35" ht="14.1" customHeight="1"/>
@@ -3435,443 +3404,443 @@
         <v>7.2.2.1.</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="5:34" ht="14.1" customHeight="1">
       <c r="E17" s="14"/>
       <c r="F17" s="17" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="5:34" ht="14.1" customHeight="1">
       <c r="F18" s="17" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="5:34" ht="14.1" customHeight="1"/>
     <row r="20" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F20" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="S20" s="20"/>
-      <c r="T20" s="20"/>
-      <c r="U20" s="20"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="20"/>
-      <c r="X20" s="20"/>
-      <c r="Y20" s="20"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="20"/>
-      <c r="AD20" s="20"/>
-      <c r="AE20" s="20"/>
-      <c r="AF20" s="20"/>
-      <c r="AG20" s="20"/>
-      <c r="AH20" s="21"/>
+      <c r="F20" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="S20" s="19"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="19"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19"/>
+      <c r="X20" s="19"/>
+      <c r="Y20" s="19"/>
+      <c r="Z20" s="19"/>
+      <c r="AA20" s="19"/>
+      <c r="AB20" s="19"/>
+      <c r="AC20" s="19"/>
+      <c r="AD20" s="19"/>
+      <c r="AE20" s="19"/>
+      <c r="AF20" s="19"/>
+      <c r="AG20" s="19"/>
+      <c r="AH20" s="20"/>
     </row>
     <row r="21" spans="5:34" ht="14.1" customHeight="1">
       <c r="F21" s="15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="16"/>
       <c r="J21" s="16"/>
       <c r="K21" s="16"/>
-      <c r="L21" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="M21" s="79"/>
-      <c r="N21" s="79"/>
-      <c r="O21" s="79"/>
-      <c r="P21" s="79"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="S21" s="22"/>
-      <c r="T21" s="22"/>
-      <c r="U21" s="22"/>
-      <c r="V21" s="22"/>
-      <c r="W21" s="22"/>
-      <c r="X21" s="22"/>
-      <c r="Y21" s="22"/>
-      <c r="Z21" s="22"/>
-      <c r="AA21" s="22"/>
-      <c r="AB21" s="22"/>
-      <c r="AC21" s="22"/>
-      <c r="AD21" s="22"/>
-      <c r="AE21" s="22"/>
-      <c r="AF21" s="22"/>
-      <c r="AG21" s="22"/>
-      <c r="AH21" s="23"/>
+      <c r="L21" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" s="56"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="56"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="S21" s="21"/>
+      <c r="T21" s="21"/>
+      <c r="U21" s="21"/>
+      <c r="V21" s="21"/>
+      <c r="W21" s="21"/>
+      <c r="X21" s="21"/>
+      <c r="Y21" s="21"/>
+      <c r="Z21" s="21"/>
+      <c r="AA21" s="21"/>
+      <c r="AB21" s="21"/>
+      <c r="AC21" s="21"/>
+      <c r="AD21" s="21"/>
+      <c r="AE21" s="21"/>
+      <c r="AF21" s="21"/>
+      <c r="AG21" s="21"/>
+      <c r="AH21" s="22"/>
     </row>
     <row r="22" spans="5:34" ht="14.1" customHeight="1">
       <c r="F22" s="15" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
       <c r="I22" s="16"/>
       <c r="J22" s="16"/>
       <c r="K22" s="16"/>
-      <c r="L22" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" s="79"/>
-      <c r="N22" s="79"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="79"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="24" t="s">
+      <c r="L22" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" s="56"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="56"/>
+      <c r="P22" s="56"/>
+      <c r="Q22" s="57"/>
+      <c r="R22" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="S22" s="21"/>
+      <c r="T22" s="21"/>
+      <c r="U22" s="21"/>
+      <c r="V22" s="21"/>
+      <c r="W22" s="21"/>
+      <c r="X22" s="21"/>
+      <c r="Y22" s="21"/>
+      <c r="Z22" s="21"/>
+      <c r="AA22" s="21"/>
+      <c r="AB22" s="21"/>
+      <c r="AC22" s="21"/>
+      <c r="AD22" s="21"/>
+      <c r="AE22" s="21"/>
+      <c r="AF22" s="21"/>
+      <c r="AG22" s="21"/>
+      <c r="AH22" s="22"/>
+    </row>
+    <row r="23" spans="5:34" ht="14.1" customHeight="1">
+      <c r="F23" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" s="56"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="56"/>
+      <c r="Q23" s="57"/>
+      <c r="R23" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="S22" s="22"/>
-      <c r="T22" s="22"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="22"/>
-      <c r="X22" s="22"/>
-      <c r="Y22" s="22"/>
-      <c r="Z22" s="22"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="22"/>
-      <c r="AC22" s="22"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="22"/>
-      <c r="AF22" s="22"/>
-      <c r="AG22" s="22"/>
-      <c r="AH22" s="23"/>
-    </row>
-    <row r="23" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F23" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" s="79"/>
-      <c r="N23" s="79"/>
-      <c r="O23" s="79"/>
-      <c r="P23" s="79"/>
-      <c r="Q23" s="80"/>
-      <c r="R23" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="S23" s="22"/>
-      <c r="T23" s="22"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="22"/>
-      <c r="X23" s="22"/>
-      <c r="Y23" s="22"/>
-      <c r="Z23" s="22"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="22"/>
-      <c r="AC23" s="22"/>
-      <c r="AD23" s="22"/>
-      <c r="AE23" s="22"/>
-      <c r="AF23" s="22"/>
-      <c r="AG23" s="22"/>
-      <c r="AH23" s="23"/>
+      <c r="S23" s="21"/>
+      <c r="T23" s="21"/>
+      <c r="U23" s="21"/>
+      <c r="V23" s="21"/>
+      <c r="W23" s="21"/>
+      <c r="X23" s="21"/>
+      <c r="Y23" s="21"/>
+      <c r="Z23" s="21"/>
+      <c r="AA23" s="21"/>
+      <c r="AB23" s="21"/>
+      <c r="AC23" s="21"/>
+      <c r="AD23" s="21"/>
+      <c r="AE23" s="21"/>
+      <c r="AF23" s="21"/>
+      <c r="AG23" s="21"/>
+      <c r="AH23" s="22"/>
     </row>
     <row r="24" spans="5:34" ht="14.1" customHeight="1">
       <c r="F24" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="79"/>
-      <c r="N24" s="79"/>
-      <c r="O24" s="79"/>
-      <c r="P24" s="79"/>
-      <c r="Q24" s="79"/>
-      <c r="R24" s="22"/>
-      <c r="S24" s="22"/>
-      <c r="T24" s="22"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="22"/>
-      <c r="W24" s="22"/>
-      <c r="X24" s="22"/>
-      <c r="Y24" s="22"/>
-      <c r="Z24" s="22"/>
-      <c r="AA24" s="22"/>
-      <c r="AB24" s="22"/>
-      <c r="AC24" s="22"/>
-      <c r="AD24" s="22"/>
-      <c r="AE24" s="22"/>
-      <c r="AF24" s="22"/>
-      <c r="AG24" s="22"/>
-      <c r="AH24" s="23"/>
+        <v>31</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="56"/>
+      <c r="P24" s="56"/>
+      <c r="Q24" s="56"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="21"/>
+      <c r="U24" s="21"/>
+      <c r="V24" s="21"/>
+      <c r="W24" s="21"/>
+      <c r="X24" s="21"/>
+      <c r="Y24" s="21"/>
+      <c r="Z24" s="21"/>
+      <c r="AA24" s="21"/>
+      <c r="AB24" s="21"/>
+      <c r="AC24" s="21"/>
+      <c r="AD24" s="21"/>
+      <c r="AE24" s="21"/>
+      <c r="AF24" s="21"/>
+      <c r="AG24" s="21"/>
+      <c r="AH24" s="22"/>
     </row>
     <row r="25" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F25" s="28"/>
-      <c r="G25" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="M25" s="79"/>
-      <c r="N25" s="79"/>
-      <c r="O25" s="79"/>
-      <c r="P25" s="79"/>
-      <c r="Q25" s="80"/>
-      <c r="R25" s="24" t="s">
+      <c r="F25" s="26"/>
+      <c r="G25" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25" s="56"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="56"/>
+      <c r="P25" s="56"/>
+      <c r="Q25" s="57"/>
+      <c r="R25" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="S25" s="21"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="21"/>
+      <c r="V25" s="21"/>
+      <c r="W25" s="21"/>
+      <c r="X25" s="21"/>
+      <c r="Y25" s="21"/>
+      <c r="Z25" s="21"/>
+      <c r="AA25" s="21"/>
+      <c r="AB25" s="21"/>
+      <c r="AC25" s="21"/>
+      <c r="AD25" s="21"/>
+      <c r="AE25" s="21"/>
+      <c r="AF25" s="21"/>
+      <c r="AG25" s="21"/>
+      <c r="AH25" s="22"/>
+    </row>
+    <row r="26" spans="5:34" ht="14.1" customHeight="1">
+      <c r="F26" s="26"/>
+      <c r="G26" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" s="56"/>
+      <c r="N26" s="56"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="56"/>
+      <c r="Q26" s="57"/>
+      <c r="R26" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="S25" s="22"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="22"/>
-      <c r="X25" s="22"/>
-      <c r="Y25" s="22"/>
-      <c r="Z25" s="22"/>
-      <c r="AA25" s="22"/>
-      <c r="AB25" s="22"/>
-      <c r="AC25" s="22"/>
-      <c r="AD25" s="22"/>
-      <c r="AE25" s="22"/>
-      <c r="AF25" s="22"/>
-      <c r="AG25" s="22"/>
-      <c r="AH25" s="23"/>
-    </row>
-    <row r="26" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F26" s="28"/>
-      <c r="G26" s="22" t="s">
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="21"/>
+      <c r="W26" s="21"/>
+      <c r="X26" s="21"/>
+      <c r="Y26" s="21"/>
+      <c r="Z26" s="21"/>
+      <c r="AA26" s="21"/>
+      <c r="AB26" s="21"/>
+      <c r="AC26" s="21"/>
+      <c r="AD26" s="21"/>
+      <c r="AE26" s="21"/>
+      <c r="AF26" s="21"/>
+      <c r="AG26" s="21"/>
+      <c r="AH26" s="22"/>
+    </row>
+    <row r="27" spans="5:34" ht="14.1" customHeight="1">
+      <c r="F27" s="26"/>
+      <c r="G27" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="56"/>
+      <c r="Q27" s="57"/>
+      <c r="R27" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="S27" s="21"/>
+      <c r="T27" s="21"/>
+      <c r="U27" s="21"/>
+      <c r="V27" s="21"/>
+      <c r="W27" s="21"/>
+      <c r="X27" s="21"/>
+      <c r="Y27" s="21"/>
+      <c r="Z27" s="21"/>
+      <c r="AA27" s="21"/>
+      <c r="AB27" s="21"/>
+      <c r="AC27" s="21"/>
+      <c r="AD27" s="21"/>
+      <c r="AE27" s="21"/>
+      <c r="AF27" s="21"/>
+      <c r="AG27" s="21"/>
+      <c r="AH27" s="22"/>
+    </row>
+    <row r="28" spans="5:34" ht="14.1" customHeight="1">
+      <c r="F28" s="26"/>
+      <c r="G28" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="M26" s="79"/>
-      <c r="N26" s="79"/>
-      <c r="O26" s="79"/>
-      <c r="P26" s="79"/>
-      <c r="Q26" s="80"/>
-      <c r="R26" s="24" t="s">
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="M28" s="56"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="56"/>
+      <c r="P28" s="56"/>
+      <c r="Q28" s="57"/>
+      <c r="R28" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="S26" s="22"/>
-      <c r="T26" s="22"/>
-      <c r="U26" s="22"/>
-      <c r="V26" s="22"/>
-      <c r="W26" s="22"/>
-      <c r="X26" s="22"/>
-      <c r="Y26" s="22"/>
-      <c r="Z26" s="22"/>
-      <c r="AA26" s="22"/>
-      <c r="AB26" s="22"/>
-      <c r="AC26" s="22"/>
-      <c r="AD26" s="22"/>
-      <c r="AE26" s="22"/>
-      <c r="AF26" s="22"/>
-      <c r="AG26" s="22"/>
-      <c r="AH26" s="23"/>
-    </row>
-    <row r="27" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F27" s="28"/>
-      <c r="G27" s="22" t="s">
+      <c r="S28" s="21"/>
+      <c r="T28" s="21"/>
+      <c r="U28" s="21"/>
+      <c r="V28" s="21"/>
+      <c r="W28" s="21"/>
+      <c r="X28" s="21"/>
+      <c r="Y28" s="21"/>
+      <c r="Z28" s="21"/>
+      <c r="AA28" s="21"/>
+      <c r="AB28" s="21"/>
+      <c r="AC28" s="21"/>
+      <c r="AD28" s="21"/>
+      <c r="AE28" s="21"/>
+      <c r="AF28" s="21"/>
+      <c r="AG28" s="21"/>
+      <c r="AH28" s="22"/>
+    </row>
+    <row r="29" spans="5:34" ht="14.1" customHeight="1">
+      <c r="F29" s="26"/>
+      <c r="G29" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="M27" s="79"/>
-      <c r="N27" s="79"/>
-      <c r="O27" s="79"/>
-      <c r="P27" s="79"/>
-      <c r="Q27" s="80"/>
-      <c r="R27" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="S27" s="22"/>
-      <c r="T27" s="22"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="22"/>
-      <c r="W27" s="22"/>
-      <c r="X27" s="22"/>
-      <c r="Y27" s="22"/>
-      <c r="Z27" s="22"/>
-      <c r="AA27" s="22"/>
-      <c r="AB27" s="22"/>
-      <c r="AC27" s="22"/>
-      <c r="AD27" s="22"/>
-      <c r="AE27" s="22"/>
-      <c r="AF27" s="22"/>
-      <c r="AG27" s="22"/>
-      <c r="AH27" s="23"/>
-    </row>
-    <row r="28" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F28" s="28"/>
-      <c r="G28" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="M28" s="79"/>
-      <c r="N28" s="79"/>
-      <c r="O28" s="79"/>
-      <c r="P28" s="79"/>
-      <c r="Q28" s="80"/>
-      <c r="R28" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="S28" s="22"/>
-      <c r="T28" s="22"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="22"/>
-      <c r="X28" s="22"/>
-      <c r="Y28" s="22"/>
-      <c r="Z28" s="22"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="22"/>
-      <c r="AC28" s="22"/>
-      <c r="AD28" s="22"/>
-      <c r="AE28" s="22"/>
-      <c r="AF28" s="22"/>
-      <c r="AG28" s="22"/>
-      <c r="AH28" s="23"/>
-    </row>
-    <row r="29" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F29" s="28"/>
-      <c r="G29" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29" s="79"/>
-      <c r="N29" s="79"/>
-      <c r="O29" s="79"/>
-      <c r="P29" s="79"/>
-      <c r="Q29" s="80"/>
-      <c r="R29" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="S29" s="22"/>
-      <c r="T29" s="22"/>
-      <c r="U29" s="22"/>
-      <c r="V29" s="22"/>
-      <c r="W29" s="22"/>
-      <c r="X29" s="22"/>
-      <c r="Y29" s="22"/>
-      <c r="Z29" s="22"/>
-      <c r="AA29" s="22"/>
-      <c r="AB29" s="22"/>
-      <c r="AC29" s="22"/>
-      <c r="AD29" s="22"/>
-      <c r="AE29" s="22"/>
-      <c r="AF29" s="22"/>
-      <c r="AG29" s="22"/>
-      <c r="AH29" s="23"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="56"/>
+      <c r="P29" s="56"/>
+      <c r="Q29" s="57"/>
+      <c r="R29" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="S29" s="21"/>
+      <c r="T29" s="21"/>
+      <c r="U29" s="21"/>
+      <c r="V29" s="21"/>
+      <c r="W29" s="21"/>
+      <c r="X29" s="21"/>
+      <c r="Y29" s="21"/>
+      <c r="Z29" s="21"/>
+      <c r="AA29" s="21"/>
+      <c r="AB29" s="21"/>
+      <c r="AC29" s="21"/>
+      <c r="AD29" s="21"/>
+      <c r="AE29" s="21"/>
+      <c r="AF29" s="21"/>
+      <c r="AG29" s="21"/>
+      <c r="AH29" s="22"/>
     </row>
     <row r="30" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F30" s="28"/>
-      <c r="G30" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" s="79"/>
-      <c r="N30" s="79"/>
-      <c r="O30" s="79"/>
-      <c r="P30" s="79"/>
-      <c r="Q30" s="80"/>
-      <c r="R30" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="S30" s="22"/>
-      <c r="T30" s="22"/>
-      <c r="U30" s="22"/>
-      <c r="V30" s="22"/>
-      <c r="W30" s="22"/>
-      <c r="X30" s="22"/>
-      <c r="Y30" s="22"/>
-      <c r="Z30" s="22"/>
-      <c r="AA30" s="22"/>
-      <c r="AB30" s="22"/>
-      <c r="AC30" s="22"/>
-      <c r="AD30" s="22"/>
-      <c r="AE30" s="22"/>
-      <c r="AF30" s="22"/>
-      <c r="AG30" s="22"/>
-      <c r="AH30" s="23"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" s="56"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="S30" s="21"/>
+      <c r="T30" s="21"/>
+      <c r="U30" s="21"/>
+      <c r="V30" s="21"/>
+      <c r="W30" s="21"/>
+      <c r="X30" s="21"/>
+      <c r="Y30" s="21"/>
+      <c r="Z30" s="21"/>
+      <c r="AA30" s="21"/>
+      <c r="AB30" s="21"/>
+      <c r="AC30" s="21"/>
+      <c r="AD30" s="21"/>
+      <c r="AE30" s="21"/>
+      <c r="AF30" s="21"/>
+      <c r="AG30" s="21"/>
+      <c r="AH30" s="22"/>
     </row>
     <row r="31" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F31" s="28"/>
+      <c r="F31" s="26"/>
       <c r="G31" s="15" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H31" s="16"/>
       <c r="I31" s="16"/>
       <c r="J31" s="16"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="M31" s="88"/>
-      <c r="N31" s="88"/>
-      <c r="O31" s="88"/>
-      <c r="P31" s="88"/>
-      <c r="Q31" s="89"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="M31" s="68"/>
+      <c r="N31" s="68"/>
+      <c r="O31" s="68"/>
+      <c r="P31" s="68"/>
+      <c r="Q31" s="69"/>
       <c r="R31" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="S31" s="16"/>
       <c r="T31" s="16"/>
@@ -3888,108 +3857,91 @@
       <c r="AE31" s="16"/>
       <c r="AF31" s="16"/>
       <c r="AG31" s="16"/>
-      <c r="AH31" s="39"/>
+      <c r="AH31" s="36"/>
     </row>
     <row r="32" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F32" s="28"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="47"/>
-      <c r="L32" s="60"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="61"/>
-      <c r="R32" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="S32" s="46"/>
-      <c r="T32" s="46"/>
-      <c r="U32" s="46"/>
-      <c r="V32" s="46"/>
-      <c r="W32" s="46"/>
-      <c r="X32" s="46"/>
-      <c r="Y32" s="46"/>
-      <c r="Z32" s="46"/>
-      <c r="AA32" s="46"/>
-      <c r="AB32" s="46"/>
-      <c r="AC32" s="46"/>
-      <c r="AD32" s="46"/>
-      <c r="AE32" s="46"/>
-      <c r="AF32" s="46"/>
-      <c r="AG32" s="46"/>
-      <c r="AH32" s="47"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="54"/>
+      <c r="R32" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="S32" s="41"/>
+      <c r="T32" s="41"/>
+      <c r="U32" s="41"/>
+      <c r="V32" s="41"/>
+      <c r="W32" s="41"/>
+      <c r="X32" s="41"/>
+      <c r="Y32" s="41"/>
+      <c r="Z32" s="41"/>
+      <c r="AA32" s="41"/>
+      <c r="AB32" s="41"/>
+      <c r="AC32" s="41"/>
+      <c r="AD32" s="41"/>
+      <c r="AE32" s="41"/>
+      <c r="AF32" s="41"/>
+      <c r="AG32" s="41"/>
+      <c r="AH32" s="43"/>
     </row>
     <row r="33" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F33" s="29"/>
-      <c r="G33" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="M33" s="79"/>
-      <c r="N33" s="79"/>
-      <c r="O33" s="79"/>
-      <c r="P33" s="79"/>
-      <c r="Q33" s="80"/>
-      <c r="R33" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="S33" s="22"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="22"/>
-      <c r="V33" s="22"/>
-      <c r="W33" s="22"/>
-      <c r="X33" s="22"/>
-      <c r="Y33" s="22"/>
-      <c r="Z33" s="22"/>
-      <c r="AA33" s="22"/>
-      <c r="AB33" s="22"/>
-      <c r="AC33" s="22"/>
-      <c r="AD33" s="22"/>
-      <c r="AE33" s="22"/>
-      <c r="AF33" s="22"/>
-      <c r="AG33" s="22"/>
-      <c r="AH33" s="23"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" s="56"/>
+      <c r="N33" s="56"/>
+      <c r="O33" s="56"/>
+      <c r="P33" s="56"/>
+      <c r="Q33" s="57"/>
+      <c r="R33" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="S33" s="21"/>
+      <c r="T33" s="21"/>
+      <c r="U33" s="21"/>
+      <c r="V33" s="21"/>
+      <c r="W33" s="21"/>
+      <c r="X33" s="21"/>
+      <c r="Y33" s="21"/>
+      <c r="Z33" s="21"/>
+      <c r="AA33" s="21"/>
+      <c r="AB33" s="21"/>
+      <c r="AC33" s="21"/>
+      <c r="AD33" s="21"/>
+      <c r="AE33" s="21"/>
+      <c r="AF33" s="21"/>
+      <c r="AG33" s="21"/>
+      <c r="AH33" s="22"/>
     </row>
     <row r="34" spans="5:34" ht="14.1" customHeight="1">
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="18"/>
-      <c r="W34" s="18"/>
-      <c r="X34" s="18"/>
-      <c r="Y34" s="18"/>
-      <c r="Z34" s="18"/>
-      <c r="AA34" s="18"/>
-      <c r="AB34" s="18"/>
-      <c r="AC34" s="18"/>
-      <c r="AD34" s="18"/>
-      <c r="AE34" s="18"/>
-      <c r="AF34" s="18"/>
-      <c r="AG34" s="18"/>
-      <c r="AH34" s="18"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24"/>
+      <c r="N34" s="24"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="24"/>
+      <c r="Q34" s="24"/>
     </row>
     <row r="35" spans="5:34" ht="14.1" customHeight="1">
       <c r="E35" s="14" t="str">
@@ -3997,228 +3949,160 @@
         <v>7.2.2.3.</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="27"/>
-      <c r="P35" s="27"/>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="18"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="18"/>
-      <c r="U35" s="18"/>
-      <c r="V35" s="18"/>
-      <c r="W35" s="18"/>
-      <c r="X35" s="18"/>
-      <c r="Y35" s="18"/>
-      <c r="Z35" s="18"/>
-      <c r="AA35" s="18"/>
-      <c r="AB35" s="18"/>
-      <c r="AC35" s="18"/>
-      <c r="AD35" s="18"/>
-      <c r="AE35" s="18"/>
-      <c r="AF35" s="18"/>
-      <c r="AG35" s="18"/>
-      <c r="AH35" s="18"/>
+        <v>47</v>
+      </c>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="24"/>
     </row>
     <row r="36" spans="5:34" ht="14.1" customHeight="1">
       <c r="E36" s="14"/>
-      <c r="F36" s="31" t="s">
-        <v>56</v>
+      <c r="F36" s="29" t="s">
+        <v>48</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="18"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="18"/>
-      <c r="U36" s="18"/>
-      <c r="V36" s="18"/>
-      <c r="W36" s="18"/>
-      <c r="X36" s="18"/>
-      <c r="Y36" s="18"/>
-      <c r="Z36" s="18"/>
-      <c r="AA36" s="18"/>
-      <c r="AB36" s="18"/>
-      <c r="AC36" s="18"/>
-      <c r="AD36" s="18"/>
-      <c r="AE36" s="18"/>
-      <c r="AF36" s="18"/>
-      <c r="AG36" s="18"/>
-      <c r="AH36" s="18"/>
+        <v>49</v>
+      </c>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="24"/>
+      <c r="N36" s="24"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="24"/>
+      <c r="Q36" s="24"/>
     </row>
     <row r="37" spans="5:34" ht="14.1" customHeight="1">
       <c r="E37" s="14"/>
-      <c r="G37" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="18"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="18"/>
-      <c r="U37" s="18"/>
-      <c r="V37" s="18"/>
-      <c r="W37" s="18"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="18"/>
-      <c r="Z37" s="18"/>
-      <c r="AA37" s="18"/>
-      <c r="AB37" s="18"/>
-      <c r="AC37" s="18"/>
-      <c r="AD37" s="18"/>
-      <c r="AE37" s="18"/>
-      <c r="AF37" s="18"/>
-      <c r="AG37" s="18"/>
-      <c r="AH37" s="18"/>
+      <c r="G37" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="24"/>
+      <c r="Q37" s="24"/>
     </row>
     <row r="38" spans="5:34" ht="14.1" customHeight="1">
       <c r="E38" s="14"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="27"/>
-      <c r="M38" s="27"/>
-      <c r="N38" s="27"/>
-      <c r="O38" s="27"/>
-      <c r="P38" s="27"/>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18"/>
-      <c r="U38" s="18"/>
-      <c r="V38" s="18"/>
-      <c r="W38" s="18"/>
-      <c r="X38" s="18"/>
-      <c r="Y38" s="18"/>
-      <c r="Z38" s="18"/>
-      <c r="AA38" s="18"/>
-      <c r="AB38" s="18"/>
-      <c r="AC38" s="18"/>
-      <c r="AD38" s="18"/>
-      <c r="AE38" s="18"/>
-      <c r="AF38" s="18"/>
-      <c r="AG38" s="18"/>
-      <c r="AH38" s="18"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24"/>
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
     </row>
     <row r="39" spans="5:34" ht="14.1" customHeight="1">
-      <c r="G39" s="19" t="s">
+      <c r="G39" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="H39" s="33" t="s">
+      <c r="H39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="O39" s="32"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="32"/>
+      <c r="X39" s="32"/>
+      <c r="Y39" s="32"/>
+      <c r="Z39" s="32"/>
+      <c r="AA39" s="32"/>
+      <c r="AB39" s="32"/>
+      <c r="AC39" s="32"/>
+      <c r="AD39" s="32"/>
+      <c r="AE39" s="32"/>
+      <c r="AF39" s="32"/>
+      <c r="AG39" s="32"/>
+      <c r="AH39" s="33"/>
+    </row>
+    <row r="40" spans="5:34" ht="14.1" customHeight="1">
+      <c r="G40" s="30">
+        <v>1</v>
+      </c>
+      <c r="H40" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="21"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="21"/>
+      <c r="M40" s="35"/>
+      <c r="N40" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="O40" s="35"/>
+      <c r="P40" s="51"/>
+      <c r="Q40" s="51"/>
+      <c r="R40" s="51"/>
+      <c r="S40" s="21"/>
+      <c r="T40" s="21"/>
+      <c r="U40" s="21"/>
+      <c r="V40" s="21"/>
+      <c r="W40" s="21"/>
+      <c r="X40" s="21"/>
+      <c r="Y40" s="21"/>
+      <c r="Z40" s="21"/>
+      <c r="AA40" s="21"/>
+      <c r="AB40" s="21"/>
+      <c r="AC40" s="21"/>
+      <c r="AD40" s="21"/>
+      <c r="AE40" s="21"/>
+      <c r="AF40" s="21"/>
+      <c r="AG40" s="21"/>
+      <c r="AH40" s="22"/>
+    </row>
+    <row r="41" spans="5:34" ht="14.1" customHeight="1">
+      <c r="G41" s="45">
+        <v>2</v>
+      </c>
+      <c r="H41" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="34"/>
-      <c r="N39" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="34"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="34"/>
-      <c r="V39" s="34"/>
-      <c r="W39" s="34"/>
-      <c r="X39" s="34"/>
-      <c r="Y39" s="34"/>
-      <c r="Z39" s="34"/>
-      <c r="AA39" s="34"/>
-      <c r="AB39" s="34"/>
-      <c r="AC39" s="34"/>
-      <c r="AD39" s="34"/>
-      <c r="AE39" s="34"/>
-      <c r="AF39" s="34"/>
-      <c r="AG39" s="34"/>
-      <c r="AH39" s="35"/>
-    </row>
-    <row r="40" spans="5:34" ht="14.1" customHeight="1">
-      <c r="G40" s="32">
-        <v>1</v>
-      </c>
-      <c r="H40" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="I40" s="37"/>
-      <c r="J40" s="38"/>
-      <c r="K40" s="38"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="38"/>
-      <c r="N40" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="O40" s="38"/>
-      <c r="P40" s="58"/>
-      <c r="Q40" s="58"/>
-      <c r="R40" s="58"/>
-      <c r="S40" s="22"/>
-      <c r="T40" s="22"/>
-      <c r="U40" s="22"/>
-      <c r="V40" s="22"/>
-      <c r="W40" s="22"/>
-      <c r="X40" s="22"/>
-      <c r="Y40" s="22"/>
-      <c r="Z40" s="22"/>
-      <c r="AA40" s="22"/>
-      <c r="AB40" s="22"/>
-      <c r="AC40" s="22"/>
-      <c r="AD40" s="22"/>
-      <c r="AE40" s="22"/>
-      <c r="AF40" s="22"/>
-      <c r="AG40" s="22"/>
-      <c r="AH40" s="23"/>
-    </row>
-    <row r="41" spans="5:34" ht="14.1" customHeight="1">
-      <c r="G41" s="50">
-        <v>2</v>
-      </c>
-      <c r="H41" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="I41" s="53"/>
-      <c r="J41" s="41"/>
-      <c r="K41" s="41"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="38"/>
       <c r="L41" s="16"/>
-      <c r="M41" s="41"/>
-      <c r="N41" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="O41" s="41"/>
-      <c r="P41" s="42"/>
-      <c r="Q41" s="42"/>
-      <c r="R41" s="42"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="O41" s="38"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="39"/>
+      <c r="R41" s="39"/>
       <c r="S41" s="16"/>
       <c r="T41" s="16"/>
       <c r="U41" s="16"/>
@@ -4234,341 +4118,192 @@
       <c r="AE41" s="16"/>
       <c r="AF41" s="16"/>
       <c r="AG41" s="16"/>
-      <c r="AH41" s="39"/>
+      <c r="AH41" s="36"/>
     </row>
     <row r="42" spans="5:34" ht="14.1" customHeight="1">
-      <c r="G42" s="55"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="51"/>
-      <c r="L42" s="46"/>
-      <c r="M42" s="52"/>
-      <c r="N42" s="54" t="s">
+      <c r="G42" s="27"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="46"/>
+      <c r="K42" s="46"/>
+      <c r="L42" s="41"/>
+      <c r="M42" s="47"/>
+      <c r="N42" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="O42" s="28"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
+      <c r="R42" s="24"/>
+      <c r="AH42" s="44"/>
+    </row>
+    <row r="43" spans="5:34" ht="14.1" customHeight="1">
+      <c r="G43" s="45">
+        <v>3</v>
+      </c>
+      <c r="H43" s="37" t="s">
         <v>58</v>
-      </c>
-      <c r="O42" s="30"/>
-      <c r="P42" s="27"/>
-      <c r="Q42" s="27"/>
-      <c r="R42" s="27"/>
-      <c r="S42" s="18"/>
-      <c r="T42" s="18"/>
-      <c r="U42" s="18"/>
-      <c r="V42" s="18"/>
-      <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
-      <c r="Y42" s="18"/>
-      <c r="Z42" s="18"/>
-      <c r="AA42" s="18"/>
-      <c r="AB42" s="18"/>
-      <c r="AC42" s="18"/>
-      <c r="AD42" s="18"/>
-      <c r="AE42" s="18"/>
-      <c r="AF42" s="18"/>
-      <c r="AG42" s="18"/>
-      <c r="AH42" s="49"/>
-    </row>
-    <row r="43" spans="5:34" ht="14.1" customHeight="1">
-      <c r="G43" s="50">
-        <v>3</v>
-      </c>
-      <c r="H43" s="40" t="s">
-        <v>53</v>
       </c>
       <c r="I43" s="16"/>
       <c r="J43" s="16"/>
       <c r="K43" s="16"/>
       <c r="L43" s="16"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="O43" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="18"/>
-      <c r="U43" s="18"/>
-      <c r="V43" s="18"/>
-      <c r="W43" s="18"/>
-      <c r="X43" s="18"/>
-      <c r="Y43" s="18"/>
-      <c r="Z43" s="18"/>
-      <c r="AA43" s="18"/>
-      <c r="AB43" s="18"/>
-      <c r="AC43" s="18"/>
-      <c r="AD43" s="18"/>
-      <c r="AE43" s="18"/>
-      <c r="AF43" s="18"/>
-      <c r="AG43" s="18"/>
-      <c r="AH43" s="49"/>
+      <c r="M43" s="36"/>
+      <c r="N43" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="O43" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="P43" s="24"/>
+      <c r="Q43" s="24"/>
+      <c r="R43" s="24"/>
+      <c r="AH43" s="44"/>
     </row>
     <row r="44" spans="5:34" ht="14.1" customHeight="1">
-      <c r="G44" s="29"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="51"/>
-      <c r="J44" s="51"/>
-      <c r="K44" s="51"/>
-      <c r="L44" s="51"/>
-      <c r="M44" s="52"/>
-      <c r="N44" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="O44" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="P44" s="45"/>
-      <c r="Q44" s="45"/>
-      <c r="R44" s="45"/>
-      <c r="S44" s="46"/>
-      <c r="T44" s="46"/>
-      <c r="U44" s="46"/>
-      <c r="V44" s="46"/>
-      <c r="W44" s="46"/>
-      <c r="X44" s="46"/>
-      <c r="Y44" s="46"/>
-      <c r="Z44" s="46"/>
-      <c r="AA44" s="46"/>
-      <c r="AB44" s="46"/>
-      <c r="AC44" s="46"/>
-      <c r="AD44" s="46"/>
-      <c r="AE44" s="46"/>
-      <c r="AF44" s="46"/>
-      <c r="AG44" s="46"/>
-      <c r="AH44" s="47"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="46"/>
+      <c r="K44" s="46"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="47"/>
+      <c r="N44" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="O44" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="41"/>
+      <c r="T44" s="41"/>
+      <c r="U44" s="41"/>
+      <c r="V44" s="41"/>
+      <c r="W44" s="41"/>
+      <c r="X44" s="41"/>
+      <c r="Y44" s="41"/>
+      <c r="Z44" s="41"/>
+      <c r="AA44" s="41"/>
+      <c r="AB44" s="41"/>
+      <c r="AC44" s="41"/>
+      <c r="AD44" s="41"/>
+      <c r="AE44" s="41"/>
+      <c r="AF44" s="41"/>
+      <c r="AG44" s="41"/>
+      <c r="AH44" s="43"/>
     </row>
     <row r="45" spans="5:34" ht="14.1" customHeight="1">
       <c r="E45" s="14"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="27"/>
-      <c r="M45" s="27"/>
-      <c r="N45" s="27"/>
-      <c r="O45" s="27"/>
-      <c r="P45" s="27"/>
-      <c r="Q45" s="27"/>
-      <c r="R45" s="18"/>
-      <c r="S45" s="18"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="18"/>
-      <c r="V45" s="18"/>
-      <c r="W45" s="18"/>
-      <c r="X45" s="18"/>
-      <c r="Y45" s="18"/>
-      <c r="Z45" s="18"/>
-      <c r="AA45" s="18"/>
-      <c r="AB45" s="18"/>
-      <c r="AC45" s="18"/>
-      <c r="AD45" s="18"/>
-      <c r="AE45" s="18"/>
-      <c r="AF45" s="18"/>
-      <c r="AG45" s="18"/>
-      <c r="AH45" s="18"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="24"/>
+      <c r="K45" s="24"/>
+      <c r="L45" s="24"/>
+      <c r="M45" s="24"/>
+      <c r="N45" s="24"/>
+      <c r="O45" s="24"/>
+      <c r="P45" s="24"/>
+      <c r="Q45" s="24"/>
     </row>
     <row r="46" spans="5:34" ht="14.1" customHeight="1">
       <c r="E46" s="14"/>
-      <c r="F46" s="31" t="s">
-        <v>56</v>
+      <c r="F46" s="29" t="s">
+        <v>48</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="18"/>
-      <c r="S46" s="18"/>
-      <c r="T46" s="18"/>
-      <c r="U46" s="18"/>
-      <c r="V46" s="18"/>
-      <c r="W46" s="18"/>
-      <c r="X46" s="18"/>
-      <c r="Y46" s="18"/>
-      <c r="Z46" s="18"/>
-      <c r="AA46" s="18"/>
-      <c r="AB46" s="18"/>
-      <c r="AC46" s="18"/>
-      <c r="AD46" s="18"/>
-      <c r="AE46" s="18"/>
-      <c r="AF46" s="18"/>
-      <c r="AG46" s="18"/>
-      <c r="AH46" s="18"/>
+        <v>61</v>
+      </c>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="24"/>
+      <c r="K46" s="24"/>
+      <c r="L46" s="24"/>
+      <c r="M46" s="24"/>
+      <c r="N46" s="24"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="24"/>
+      <c r="Q46" s="24"/>
     </row>
     <row r="47" spans="5:34" ht="14.1" customHeight="1">
       <c r="E47" s="14"/>
-      <c r="F47" s="31"/>
+      <c r="F47" s="29"/>
       <c r="G47" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
-      <c r="K47" s="27"/>
-      <c r="L47" s="27"/>
-      <c r="M47" s="27"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="27"/>
-      <c r="P47" s="27"/>
-      <c r="Q47" s="27"/>
-      <c r="R47" s="18"/>
-      <c r="S47" s="18"/>
-      <c r="T47" s="18"/>
-      <c r="U47" s="18"/>
-      <c r="V47" s="18"/>
-      <c r="W47" s="18"/>
-      <c r="X47" s="18"/>
-      <c r="Y47" s="18"/>
-      <c r="Z47" s="18"/>
-      <c r="AA47" s="18"/>
-      <c r="AB47" s="18"/>
-      <c r="AC47" s="18"/>
-      <c r="AD47" s="18"/>
-      <c r="AE47" s="18"/>
-      <c r="AF47" s="18"/>
-      <c r="AG47" s="18"/>
-      <c r="AH47" s="18"/>
+        <v>62</v>
+      </c>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="24"/>
+      <c r="K47" s="24"/>
+      <c r="L47" s="24"/>
+      <c r="M47" s="24"/>
+      <c r="N47" s="24"/>
+      <c r="O47" s="24"/>
+      <c r="P47" s="24"/>
+      <c r="Q47" s="24"/>
     </row>
     <row r="48" spans="5:34" ht="14.1" customHeight="1">
       <c r="E48" s="14"/>
-      <c r="F48" s="31"/>
+      <c r="F48" s="29"/>
       <c r="G48" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="H48" s="27"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="27"/>
-      <c r="K48" s="27"/>
-      <c r="L48" s="27"/>
-      <c r="M48" s="27"/>
-      <c r="N48" s="27"/>
-      <c r="O48" s="27"/>
-      <c r="P48" s="27"/>
-      <c r="Q48" s="27"/>
-      <c r="R48" s="18"/>
-      <c r="S48" s="18"/>
-      <c r="T48" s="18"/>
-      <c r="U48" s="18"/>
-      <c r="V48" s="18"/>
-      <c r="W48" s="18"/>
-      <c r="X48" s="18"/>
-      <c r="Y48" s="18"/>
-      <c r="Z48" s="18"/>
-      <c r="AA48" s="18"/>
-      <c r="AB48" s="18"/>
-      <c r="AC48" s="18"/>
-      <c r="AD48" s="18"/>
-      <c r="AE48" s="18"/>
-      <c r="AF48" s="18"/>
-      <c r="AG48" s="18"/>
-      <c r="AH48" s="18"/>
+        <v>63</v>
+      </c>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="24"/>
+      <c r="M48" s="24"/>
+      <c r="N48" s="24"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="24"/>
+      <c r="Q48" s="24"/>
     </row>
     <row r="49" spans="4:34" ht="14.1" customHeight="1">
       <c r="E49" s="14"/>
-      <c r="F49" s="31"/>
+      <c r="F49" s="29"/>
       <c r="G49" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="Q49" s="27"/>
-      <c r="R49" s="18"/>
-      <c r="S49" s="18"/>
-      <c r="T49" s="18"/>
-      <c r="U49" s="18"/>
-      <c r="V49" s="18"/>
-      <c r="W49" s="18"/>
-      <c r="X49" s="18"/>
-      <c r="Y49" s="18"/>
-      <c r="Z49" s="18"/>
-      <c r="AA49" s="18"/>
-      <c r="AB49" s="18"/>
-      <c r="AC49" s="18"/>
-      <c r="AD49" s="18"/>
-      <c r="AE49" s="18"/>
-      <c r="AF49" s="18"/>
-      <c r="AG49" s="18"/>
-      <c r="AH49" s="18"/>
+        <v>64</v>
+      </c>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="24"/>
+      <c r="K49" s="24"/>
+      <c r="L49" s="24"/>
+      <c r="M49" s="24"/>
+      <c r="N49" s="24"/>
+      <c r="O49" s="24"/>
+      <c r="P49" s="24"/>
+      <c r="Q49" s="24"/>
     </row>
     <row r="50" spans="4:34" ht="14.1" customHeight="1">
       <c r="E50" s="14"/>
       <c r="G50" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="H50" s="27"/>
-      <c r="I50" s="27"/>
-      <c r="J50" s="27"/>
-      <c r="K50" s="27"/>
-      <c r="L50" s="27"/>
-      <c r="M50" s="27"/>
-      <c r="N50" s="27"/>
-      <c r="O50" s="27"/>
-      <c r="P50" s="27"/>
-      <c r="Q50" s="27"/>
-      <c r="R50" s="18"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="18"/>
-      <c r="U50" s="18"/>
-      <c r="V50" s="18"/>
-      <c r="W50" s="18"/>
-      <c r="X50" s="18"/>
-      <c r="Y50" s="18"/>
-      <c r="Z50" s="18"/>
-      <c r="AA50" s="18"/>
-      <c r="AB50" s="18"/>
-      <c r="AC50" s="18"/>
-      <c r="AD50" s="18"/>
-      <c r="AE50" s="18"/>
-      <c r="AF50" s="18"/>
-      <c r="AG50" s="18"/>
-      <c r="AH50" s="18"/>
+        <v>65</v>
+      </c>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="24"/>
+      <c r="K50" s="24"/>
+      <c r="L50" s="24"/>
+      <c r="M50" s="24"/>
+      <c r="N50" s="24"/>
+      <c r="O50" s="24"/>
+      <c r="P50" s="24"/>
+      <c r="Q50" s="24"/>
     </row>
     <row r="51" spans="4:34" ht="14.1" customHeight="1">
-      <c r="I51" s="27"/>
-      <c r="J51" s="27"/>
-      <c r="K51" s="27"/>
-      <c r="L51" s="27"/>
-      <c r="M51" s="27"/>
-      <c r="N51" s="27"/>
-      <c r="O51" s="27"/>
-      <c r="P51" s="27"/>
-      <c r="Q51" s="27"/>
-      <c r="R51" s="18"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="18"/>
-      <c r="U51" s="18"/>
-      <c r="V51" s="18"/>
-      <c r="W51" s="18"/>
-      <c r="X51" s="18"/>
-      <c r="Y51" s="18"/>
-      <c r="Z51" s="18"/>
-      <c r="AA51" s="18"/>
-      <c r="AB51" s="18"/>
-      <c r="AC51" s="18"/>
-      <c r="AD51" s="18"/>
-      <c r="AE51" s="18"/>
-      <c r="AF51" s="18"/>
-      <c r="AG51" s="18"/>
-      <c r="AH51" s="18"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="24"/>
+      <c r="K51" s="24"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="24"/>
+      <c r="N51" s="24"/>
+      <c r="O51" s="24"/>
+      <c r="P51" s="24"/>
+      <c r="Q51" s="24"/>
     </row>
     <row r="52" spans="4:34" ht="14.1" customHeight="1">
       <c r="D52" s="14" t="str">
@@ -4576,7 +4311,7 @@
         <v>7.2.3.</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="4:34" ht="14.1" customHeight="1"/>
@@ -4586,90 +4321,98 @@
         <v>7.2.3.1.</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="4:34" ht="14.1" customHeight="1">
       <c r="F55" s="17" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="4:34" ht="14.1" customHeight="1">
-      <c r="F56" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="20"/>
-      <c r="L56" s="21"/>
-      <c r="M56" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="N56" s="20"/>
-      <c r="O56" s="20"/>
-      <c r="P56" s="20"/>
-      <c r="Q56" s="20"/>
-      <c r="R56" s="20"/>
-      <c r="S56" s="21"/>
-      <c r="T56" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="U56" s="20"/>
-      <c r="V56" s="20"/>
-      <c r="W56" s="20"/>
-      <c r="X56" s="20"/>
-      <c r="Y56" s="20"/>
-      <c r="Z56" s="20"/>
-      <c r="AA56" s="20"/>
-      <c r="AB56" s="20"/>
-      <c r="AC56" s="20"/>
-      <c r="AD56" s="20"/>
-      <c r="AE56" s="20"/>
-      <c r="AF56" s="20"/>
-      <c r="AG56" s="20"/>
-      <c r="AH56" s="21"/>
+      <c r="F56" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="G56" s="19"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="19"/>
+      <c r="K56" s="19"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="N56" s="19"/>
+      <c r="O56" s="19"/>
+      <c r="P56" s="19"/>
+      <c r="Q56" s="19"/>
+      <c r="R56" s="19"/>
+      <c r="S56" s="20"/>
+      <c r="T56" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="U56" s="19"/>
+      <c r="V56" s="19"/>
+      <c r="W56" s="19"/>
+      <c r="X56" s="19"/>
+      <c r="Y56" s="19"/>
+      <c r="Z56" s="19"/>
+      <c r="AA56" s="19"/>
+      <c r="AB56" s="19"/>
+      <c r="AC56" s="19"/>
+      <c r="AD56" s="19"/>
+      <c r="AE56" s="19"/>
+      <c r="AF56" s="19"/>
+      <c r="AG56" s="19"/>
+      <c r="AH56" s="20"/>
     </row>
     <row r="57" spans="4:34" ht="14.25" customHeight="1">
-      <c r="F57" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
-      <c r="J57" s="22"/>
-      <c r="K57" s="22"/>
-      <c r="L57" s="23"/>
-      <c r="M57" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="N57" s="22"/>
-      <c r="O57" s="22"/>
-      <c r="P57" s="22"/>
-      <c r="Q57" s="22"/>
-      <c r="R57" s="22"/>
-      <c r="S57" s="23"/>
-      <c r="T57" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="U57" s="22"/>
-      <c r="V57" s="22"/>
-      <c r="W57" s="22"/>
-      <c r="X57" s="22"/>
-      <c r="Y57" s="22"/>
-      <c r="Z57" s="22"/>
-      <c r="AA57" s="22"/>
-      <c r="AB57" s="22"/>
-      <c r="AC57" s="22"/>
-      <c r="AD57" s="22"/>
-      <c r="AE57" s="22"/>
-      <c r="AF57" s="22"/>
-      <c r="AG57" s="22"/>
-      <c r="AH57" s="23"/>
+      <c r="F57" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="21"/>
+      <c r="K57" s="21"/>
+      <c r="L57" s="22"/>
+      <c r="M57" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="N57" s="21"/>
+      <c r="O57" s="21"/>
+      <c r="P57" s="21"/>
+      <c r="Q57" s="21"/>
+      <c r="R57" s="21"/>
+      <c r="S57" s="22"/>
+      <c r="T57" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="U57" s="21"/>
+      <c r="V57" s="21"/>
+      <c r="W57" s="21"/>
+      <c r="X57" s="21"/>
+      <c r="Y57" s="21"/>
+      <c r="Z57" s="21"/>
+      <c r="AA57" s="21"/>
+      <c r="AB57" s="21"/>
+      <c r="AC57" s="21"/>
+      <c r="AD57" s="21"/>
+      <c r="AE57" s="21"/>
+      <c r="AF57" s="21"/>
+      <c r="AG57" s="21"/>
+      <c r="AH57" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="AF1:AI1"/>
+    <mergeCell ref="E2:O2"/>
+    <mergeCell ref="R2:X3"/>
+    <mergeCell ref="AA2:AE2"/>
+    <mergeCell ref="AF2:AI2"/>
+    <mergeCell ref="E3:O3"/>
+    <mergeCell ref="AA3:AE3"/>
+    <mergeCell ref="AF3:AI3"/>
     <mergeCell ref="L33:Q33"/>
     <mergeCell ref="L26:Q26"/>
     <mergeCell ref="E1:O1"/>
@@ -4685,14 +4428,6 @@
     <mergeCell ref="L23:Q23"/>
     <mergeCell ref="L24:Q24"/>
     <mergeCell ref="L31:Q31"/>
-    <mergeCell ref="AF1:AI1"/>
-    <mergeCell ref="E2:O2"/>
-    <mergeCell ref="R2:X3"/>
-    <mergeCell ref="AA2:AE2"/>
-    <mergeCell ref="AF2:AI2"/>
-    <mergeCell ref="E3:O3"/>
-    <mergeCell ref="AA3:AE3"/>
-    <mergeCell ref="AF3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
